--- a/Requirements Analysis/Requirements.xlsx
+++ b/Requirements Analysis/Requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nps01-my.sharepoint.com/personal/luke_smith_nps_edu/Documents/Documents/GitHub/SE4003-Capstone-U2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_F25DC773A252ABDACC104892715C7D4C5BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAD4ADA8-E7D6-4ABA-8531-FA752CFDE46A}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_F25DC773A252ABDACC104892715C7D4C5BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6684F4AD-9FFE-432E-B6EE-BC8F8121D59B}"/>
   <bookViews>
     <workbookView xWindow="1725" yWindow="2685" windowWidth="13080" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Text</t>
   </si>
   <si>
-    <t>Functional?</t>
+    <t>Functional</t>
   </si>
   <si>
     <t>ROS-based System</t>
@@ -56,25 +56,37 @@
     <t>The system shall be controlled by ROS software</t>
   </si>
   <si>
+    <t>Non-Functional</t>
+  </si>
+  <si>
     <t>Python Language</t>
   </si>
   <si>
     <t>The programming language of the system shall be python</t>
   </si>
   <si>
-    <t>Documentation</t>
-  </si>
-  <si>
     <t>Simulation</t>
   </si>
   <si>
-    <t>The system shall operate simulation environment</t>
+    <t>The system shall operate in simulation environment</t>
   </si>
   <si>
     <t>iRobot Platform</t>
   </si>
   <si>
-    <t>The system proof of concept shall be a iRobot compatible Roomba</t>
+    <t>The system proof of concept software shall be executed by iRobot Open Interface compatible Roomba</t>
+  </si>
+  <si>
+    <t>ROS Nodes</t>
+  </si>
+  <si>
+    <t>The system shall consist of ROS nodes</t>
+  </si>
+  <si>
+    <t>ROS Topics Documentation</t>
+  </si>
+  <si>
+    <t>The system internal interfaces shall be documented topics or service</t>
   </si>
   <si>
     <t>ROS Topics</t>
@@ -83,31 +95,16 @@
     <t>The system shall subscribe and publish to relevant ROS topics</t>
   </si>
   <si>
-    <t>ROS Nodes</t>
-  </si>
-  <si>
-    <t>The system shall consist of ROS nodes</t>
-  </si>
-  <si>
-    <t>ROS Topics Documentation</t>
-  </si>
-  <si>
-    <t>The system internal interfaces shall be documented topics or services when passing information between nodes</t>
-  </si>
-  <si>
     <t>ROS Position</t>
   </si>
   <si>
     <t>The system shall determine position relative to start while exploring</t>
   </si>
   <si>
-    <t>ROS Services</t>
-  </si>
-  <si>
     <t>ROS Map</t>
   </si>
   <si>
-    <t>The system shall determine topography of room</t>
+    <t>The system shall map topography of room</t>
   </si>
   <si>
     <t>ROS Log</t>
@@ -119,7 +116,7 @@
     <t>Wall</t>
   </si>
   <si>
-    <t>The system shall detect vertical obstacles of at least {} cm</t>
+    <t>The system shall detect vertical obstacles of at least {XX} cm</t>
   </si>
   <si>
     <t>Terrain</t>
@@ -137,7 +134,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>The system shall report completion or termination of task</t>
+    <t>The system shall report completion or termination of assigned tasks</t>
   </si>
   <si>
     <t>Stuck</t>
@@ -179,8 +176,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,10 +461,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="61.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -474,7 +475,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -482,133 +483,213 @@
       </c>
     </row>
     <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30.75">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="B4" t="s">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="B5" t="s">
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6" t="s">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30.75">
+      <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7" t="s">
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8" t="s">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30.75">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
       <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" t="s">
+      <c r="C16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C18" t="s">
-        <v>35</v>
+      <c r="D16" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
